--- a/idecba/shoppings.xlsx
+++ b/idecba/shoppings.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8505"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22875" windowHeight="8580"/>
   </bookViews>
   <sheets>
     <sheet name="AC_CC_AX07" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="56">
   <si>
     <t>Período</t>
   </si>
@@ -302,7 +302,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t>). Ciudad de Buenos Aires. Enero 2014/junio 2026</t>
+      <t>). Ciudad de Buenos Aires. Enero 2014/julio 2026</t>
     </r>
   </si>
 </sst>
@@ -1104,14 +1104,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L183"/>
+  <dimension ref="A1:L184"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.625" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.625" style="1"/>
     <col min="2" max="2" width="11.625" style="5" customWidth="1"/>
     <col min="3" max="3" width="10.625" style="5"/>
     <col min="4" max="4" width="13.125" style="5" customWidth="1"/>
-    <col min="5" max="8" width="10.625" style="5"/>
+    <col min="5" max="5" width="10.625" style="5"/>
+    <col min="6" max="6" width="13.625" style="5" customWidth="1"/>
+    <col min="7" max="8" width="10.625" style="5"/>
     <col min="9" max="9" width="12" style="5" customWidth="1"/>
     <col min="10" max="11" width="10.625" style="5"/>
     <col min="12" max="16384" width="10.625" style="1"/>
@@ -6847,72 +6849,94 @@
       </c>
     </row>
     <row r="167" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A167" s="23" t="s">
+      <c r="A167" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B167" s="30">
+      <c r="B167" s="35">
         <v>-3.6078468416862131</v>
       </c>
-      <c r="C167" s="30">
+      <c r="C167" s="35">
         <v>24.151078709736208</v>
       </c>
-      <c r="D167" s="30">
+      <c r="D167" s="35">
         <v>143.44835271514577</v>
       </c>
-      <c r="E167" s="30">
+      <c r="E167" s="35">
         <v>-4.4299175203395214</v>
       </c>
-      <c r="F167" s="30">
+      <c r="F167" s="35">
         <v>-13.528216791591808</v>
       </c>
-      <c r="G167" s="30">
+      <c r="G167" s="35">
         <v>-10.689152894469656</v>
       </c>
-      <c r="H167" s="30">
+      <c r="H167" s="35">
         <v>-19.841171670565348</v>
       </c>
-      <c r="I167" s="30">
+      <c r="I167" s="35">
         <v>-3.9629145947990496</v>
       </c>
-      <c r="J167" s="30">
+      <c r="J167" s="35">
         <v>-4.7313458379755646</v>
       </c>
-      <c r="K167" s="30">
+      <c r="K167" s="35">
         <v>-13.758355651091215</v>
       </c>
     </row>
     <row r="168" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
-      <c r="A168" s="24" t="s">
+      <c r="A168" s="23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B168" s="30">
+        <v>3.782257408574119</v>
+      </c>
+      <c r="C168" s="30">
+        <v>36.017060120585029</v>
+      </c>
+      <c r="D168" s="30">
+        <v>139.75703150857802</v>
+      </c>
+      <c r="E168" s="30">
+        <v>-4.2985510938631339</v>
+      </c>
+      <c r="F168" s="30">
+        <v>-18.661284014067757</v>
+      </c>
+      <c r="G168" s="30">
+        <v>2.7452919684091359</v>
+      </c>
+      <c r="H168" s="30">
+        <v>-13.562993041422832</v>
+      </c>
+      <c r="I168" s="30">
+        <v>9.0300827954161491</v>
+      </c>
+      <c r="J168" s="30">
+        <v>-10.315922776196595</v>
+      </c>
+      <c r="K168" s="30">
+        <v>-6.4723357436384132</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A169" s="24" t="s">
         <v>52</v>
       </c>
-      <c r="B168" s="25"/>
-      <c r="C168" s="25"/>
-      <c r="D168" s="25"/>
-      <c r="E168" s="21"/>
-      <c r="F168" s="21"/>
-      <c r="G168" s="21"/>
-      <c r="H168" s="21"/>
-      <c r="I168" s="21"/>
-      <c r="J168" s="21"/>
-      <c r="K168" s="21"/>
-    </row>
-    <row r="169" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A169" s="42" t="s">
+      <c r="B169" s="25"/>
+      <c r="C169" s="25"/>
+      <c r="D169" s="25"/>
+      <c r="E169" s="21"/>
+      <c r="F169" s="21"/>
+      <c r="G169" s="21"/>
+      <c r="H169" s="21"/>
+      <c r="I169" s="21"/>
+      <c r="J169" s="21"/>
+      <c r="K169" s="21"/>
+    </row>
+    <row r="170" spans="1:11" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="B169" s="42"/>
-      <c r="C169" s="42"/>
-      <c r="D169" s="42"/>
-      <c r="E169" s="42"/>
-      <c r="F169" s="42"/>
-      <c r="G169" s="42"/>
-      <c r="H169" s="42"/>
-      <c r="I169" s="42"/>
-      <c r="J169" s="42"/>
-      <c r="K169" s="42"/>
-    </row>
-    <row r="170" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A170" s="42"/>
       <c r="B170" s="42"/>
       <c r="C170" s="42"/>
       <c r="D170" s="42"/>
@@ -6924,17 +6948,18 @@
       <c r="J170" s="42"/>
       <c r="K170" s="42"/>
     </row>
-    <row r="178" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B178" s="1"/>
-      <c r="C178" s="1"/>
-      <c r="D178" s="1"/>
-      <c r="E178" s="1"/>
-      <c r="F178" s="1"/>
-      <c r="G178" s="1"/>
-      <c r="H178" s="1"/>
-      <c r="I178" s="1"/>
-      <c r="J178" s="1"/>
-      <c r="K178" s="1"/>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A171" s="42"/>
+      <c r="B171" s="42"/>
+      <c r="C171" s="42"/>
+      <c r="D171" s="42"/>
+      <c r="E171" s="42"/>
+      <c r="F171" s="42"/>
+      <c r="G171" s="42"/>
+      <c r="H171" s="42"/>
+      <c r="I171" s="42"/>
+      <c r="J171" s="42"/>
+      <c r="K171" s="42"/>
     </row>
     <row r="179" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B179" s="1"/>
@@ -6996,12 +7021,24 @@
       <c r="J183" s="1"/>
       <c r="K183" s="1"/>
     </row>
+    <row r="184" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="B184" s="1"/>
+      <c r="C184" s="1"/>
+      <c r="D184" s="1"/>
+      <c r="E184" s="1"/>
+      <c r="F184" s="1"/>
+      <c r="G184" s="1"/>
+      <c r="H184" s="1"/>
+      <c r="I184" s="1"/>
+      <c r="J184" s="1"/>
+      <c r="K184" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:K2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A169:K170"/>
+    <mergeCell ref="A170:K171"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -7029,7 +7066,7 @@
       </c>
       <c r="B1" s="44"/>
     </row>
-    <row r="2" spans="1:8" ht="13.5" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>26</v>
       </c>
@@ -7037,7 +7074,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="17.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>28</v>
       </c>
@@ -7061,7 +7098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="42" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="38.25" x14ac:dyDescent="0.2">
       <c r="A6" s="32" t="s">
         <v>34</v>
       </c>
@@ -7085,7 +7122,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="51" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="54.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
@@ -7112,7 +7149,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="12" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="33" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>43</v>
       </c>
@@ -7120,7 +7157,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="35.1" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>50</v>
       </c>
